--- a/data/trans_bre/P2C_R-Edad-trans_bre.xlsx
+++ b/data/trans_bre/P2C_R-Edad-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-9,18; 9,89</t>
+          <t>-8,89; 9,83</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-4,81; 6,12</t>
+          <t>-4,7; 5,98</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-2,96; 8,93</t>
+          <t>-3,62; 8,98</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-23,16; 4,81</t>
+          <t>-22,81; 3,97</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-10,32; 12,73</t>
+          <t>-10,17; 12,82</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-4,94; 6,77</t>
+          <t>-4,91; 6,58</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-3,1; 10,2</t>
+          <t>-3,83; 10,26</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-39,08; 9,53</t>
+          <t>-38,59; 8,25</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-3,73; 9,1</t>
+          <t>-3,19; 8,31</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-0,27; 7,44</t>
+          <t>-0,12; 7,71</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-8,11; 3,12</t>
+          <t>-7,55; 3,92</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-15,1; 2,42</t>
+          <t>-15,13; 2,39</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-4,37; 11,48</t>
+          <t>-3,75; 10,35</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-0,27; 8,36</t>
+          <t>-0,11; 8,75</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-8,97; 3,55</t>
+          <t>-8,46; 4,56</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-33,57; 6,76</t>
+          <t>-34,52; 6,0</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-14,9; 6,78</t>
+          <t>-15,75; 6,93</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-3,04; 11,79</t>
+          <t>-2,88; 12,4</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-9,83; 8,64</t>
+          <t>-9,34; 8,76</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-3,59; 13,58</t>
+          <t>-3,59; 13,0</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-20,23; 10,71</t>
+          <t>-21,03; 10,71</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-3,67; 14,04</t>
+          <t>-3,33; 15,18</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-12,5; 12,39</t>
+          <t>-11,63; 12,98</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-10,94; 60,27</t>
+          <t>-13,33; 54,7</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-6,63; 11,79</t>
+          <t>-6,93; 11,87</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-9,19; 7,46</t>
+          <t>-10,51; 7,81</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-16,59; 3,4</t>
+          <t>-16,56; 3,84</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-16,01; 3,47</t>
+          <t>-16,27; 3,91</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-13,96; 30,64</t>
+          <t>-14,75; 31,19</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-11,16; 10,14</t>
+          <t>-12,59; 10,4</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-34,36; 7,26</t>
+          <t>-33,66; 9,28</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-45,84; 13,43</t>
+          <t>-47,78; 17,68</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-3,58; 5,57</t>
+          <t>-3,89; 5,29</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,15; 5,38</t>
+          <t>-1,04; 5,12</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-6,82; 1,97</t>
+          <t>-6,77; 1,68</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-8,87; 1,9</t>
+          <t>-8,75; 1,73</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-5,07; 8,48</t>
+          <t>-5,51; 7,88</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-1,3; 6,26</t>
+          <t>-1,15; 5,97</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-8,78; 2,65</t>
+          <t>-8,81; 2,28</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-24,98; 6,44</t>
+          <t>-24,71; 5,86</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P2C_R-Edad-trans_bre.xlsx
+++ b/data/trans_bre/P2C_R-Edad-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-8,89; 9,83</t>
+          <t>-7,98; 10,98</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-4,7; 5,98</t>
+          <t>-4,85; 5,57</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-3,62; 8,98</t>
+          <t>-3,0; 8,67</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-22,81; 3,97</t>
+          <t>-23,68; 4,47</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-10,17; 12,82</t>
+          <t>-9,21; 14,38</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-4,91; 6,58</t>
+          <t>-5,04; 6,13</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-3,83; 10,26</t>
+          <t>-3,14; 10,18</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-38,59; 8,25</t>
+          <t>-39,06; 8,86</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-3,19; 8,31</t>
+          <t>-3,07; 8,97</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-0,12; 7,71</t>
+          <t>-0,29; 8,2</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-7,55; 3,92</t>
+          <t>-7,96; 3,57</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-15,13; 2,39</t>
+          <t>-16,08; 1,02</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-3,75; 10,35</t>
+          <t>-3,6; 11,45</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-0,11; 8,75</t>
+          <t>-0,3; 9,31</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-8,46; 4,56</t>
+          <t>-8,75; 4,15</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-34,52; 6,0</t>
+          <t>-34,77; 3,21</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-15,75; 6,93</t>
+          <t>-15,81; 7,22</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,88; 12,4</t>
+          <t>-3,12; 11,91</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-9,34; 8,76</t>
+          <t>-8,97; 8,7</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-3,59; 13,0</t>
+          <t>-4,07; 12,83</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-21,03; 10,71</t>
+          <t>-21,71; 11,41</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-3,33; 15,18</t>
+          <t>-3,67; 14,45</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-11,63; 12,98</t>
+          <t>-11,79; 12,54</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-13,33; 54,7</t>
+          <t>-13,1; 56,05</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-6,93; 11,87</t>
+          <t>-6,52; 12,02</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-10,51; 7,81</t>
+          <t>-10,21; 6,96</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-16,56; 3,84</t>
+          <t>-16,45; 4,95</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-16,27; 3,91</t>
+          <t>-15,13; 4,17</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-14,75; 31,19</t>
+          <t>-13,28; 32,4</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-12,59; 10,4</t>
+          <t>-12,68; 9,36</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-33,66; 9,28</t>
+          <t>-33,04; 14,03</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-47,78; 17,68</t>
+          <t>-46,87; 16,31</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-3,89; 5,29</t>
+          <t>-4,02; 5,44</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,04; 5,12</t>
+          <t>-1,18; 5,29</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-6,77; 1,68</t>
+          <t>-6,67; 1,69</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-8,75; 1,73</t>
+          <t>-8,24; 1,77</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-5,51; 7,88</t>
+          <t>-5,65; 8,22</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-1,15; 5,97</t>
+          <t>-1,35; 6,15</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-8,81; 2,28</t>
+          <t>-8,56; 2,29</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-24,71; 5,86</t>
+          <t>-23,78; 5,78</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P2C_R-Edad-trans_bre.xlsx
+++ b/data/trans_bre/P2C_R-Edad-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-9,38</t>
+          <t>-10,75</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>-17,53%</t>
+          <t>-20,23%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-7,98; 10,98</t>
+          <t>-9,18; 9,89</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-4,85; 5,57</t>
+          <t>-4,81; 6,12</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-3,0; 8,67</t>
+          <t>-2,96; 8,93</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-23,68; 4,47</t>
+          <t>-24,17; 3,36</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-9,21; 14,38</t>
+          <t>-10,32; 12,73</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-5,04; 6,13</t>
+          <t>-4,94; 6,77</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-3,14; 10,18</t>
+          <t>-3,1; 10,2</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-39,06; 8,86</t>
+          <t>-41,33; 6,99</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-6,97</t>
+          <t>-5,96</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>-17,12%</t>
+          <t>-14,42%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-3,07; 8,97</t>
+          <t>-3,73; 9,1</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-0,29; 8,2</t>
+          <t>-0,27; 7,44</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-7,96; 3,57</t>
+          <t>-8,11; 3,12</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-16,08; 1,02</t>
+          <t>-14,3; 3,39</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-3,6; 11,45</t>
+          <t>-4,37; 11,48</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-0,3; 9,31</t>
+          <t>-0,27; 8,36</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-8,75; 4,15</t>
+          <t>-8,97; 3,55</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-34,77; 3,21</t>
+          <t>-31,22; 9,8</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>4,57</t>
+          <t>4,37</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>16,71%</t>
+          <t>14,82%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-15,81; 7,22</t>
+          <t>-14,9; 6,78</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-3,12; 11,91</t>
+          <t>-3,04; 11,79</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-8,97; 8,7</t>
+          <t>-9,83; 8,64</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-4,07; 12,83</t>
+          <t>-4,21; 13,23</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-21,71; 11,41</t>
+          <t>-20,23; 10,71</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-3,67; 14,45</t>
+          <t>-3,67; 14,04</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-11,79; 12,54</t>
+          <t>-12,5; 12,39</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-13,1; 56,05</t>
+          <t>-12,58; 54,95</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-5,14</t>
+          <t>-5,36</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-18,3%</t>
+          <t>-18,15%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-6,52; 12,02</t>
+          <t>-6,63; 11,79</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-10,21; 6,96</t>
+          <t>-9,19; 7,46</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-16,45; 4,95</t>
+          <t>-16,59; 3,4</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-15,13; 4,17</t>
+          <t>-15,01; 1,67</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-13,28; 32,4</t>
+          <t>-13,96; 30,64</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-12,68; 9,36</t>
+          <t>-11,16; 10,14</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-33,04; 14,03</t>
+          <t>-34,36; 7,26</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-46,87; 16,31</t>
+          <t>-41,42; 6,78</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-3,26</t>
+          <t>-2,9</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>-9,88%</t>
+          <t>-8,57%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-4,02; 5,44</t>
+          <t>-3,58; 5,57</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,18; 5,29</t>
+          <t>-1,15; 5,38</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-6,67; 1,69</t>
+          <t>-6,82; 1,97</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-8,24; 1,77</t>
+          <t>-7,7; 1,98</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-5,65; 8,22</t>
+          <t>-5,07; 8,48</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-1,35; 6,15</t>
+          <t>-1,3; 6,26</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-8,56; 2,29</t>
+          <t>-8,78; 2,65</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-23,78; 5,78</t>
+          <t>-21,63; 6,09</t>
         </is>
       </c>
     </row>
